--- a/04_DESIGN_TABLES/DesignTable_5500.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5500.xlsx
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.44</v>
@@ -586,10 +586,14 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s127 only (double-pass 29 rows)</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
+          <t>Air-Way s127 only (double-pass 29 rows); N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]; N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 2 settled): N1@DRIVE 0.72 -&gt; OMi 0.780 (Items!N1432, M099) | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.72 -&gt; OMi 0.780 (Items!P1432, M100)</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -698,7 +702,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -706,7 +710,11 @@
           <t>Air-Way s127 only (double-pass 29 rows)</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.09~1.090; N2@DRIVE=0.9~0.900; Y@REF=0.56~0.562; D1@BORE=0.28~0.281; D2@BORE=0.19~0.188</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -815,7 +823,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -823,7 +831,11 @@
           <t>Air-Way s127 only (double-pass 29 rows)</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.09~1.090; N2@DRIVE=1.09~1.090; Y@REF=0.56~0.562; D1@BORE=0.28~0.281; D2@BORE=0.28~0.281</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -932,7 +944,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -940,7 +952,11 @@
           <t>Air-Way s127 only (double-pass 29 rows)</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.22~1.220; N2@DRIVE=1.22~1.220; Y@REF=0.75~0.750; D1@BORE=0.41~0.406; D2@BORE=0.28~0.281</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1049,7 +1065,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -1057,7 +1073,11 @@
           <t>Air-Way s127 only (double-pass 29 rows)</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.22~1.220; N2@DRIVE=1.22~1.220; Y@REF=0.75~0.750; D1@BORE=0.41~0.406; D2@BORE=0.41~0.406</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1224,7 +1244,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -1232,7 +1252,11 @@
           <t>Air-Way s127 only (double-pass 29 rows)</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.47~1.470; N2@DRIVE=1.28~1.280; Y@REF=0.88~0.875; D1@BORE=0.53~0.531; D2@BORE=0.41~0.406</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1341,7 +1365,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1349,7 +1373,11 @@
           <t>Air-Way s127 only (double-pass 29 rows)</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.47~1.470; N2@DRIVE=1.47~1.470; Y@REF=0.88~0.875; D1@BORE=0.53~0.531; D2@BORE=0.53~0.531</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1574,7 +1602,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
@@ -1582,7 +1610,11 @@
           <t>Air-Way s127 only (double-pass 29 rows)</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr"/>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.59~1.590; N2@DRIVE=1.59~1.590; Y@REF=1.06~1.062; D1@BORE=0.72~0.719; D2@BORE=0.53~0.531</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1633,7 +1665,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -1641,7 +1673,11 @@
           <t>Air-Way s127 only (double-pass 29 rows)</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.59~1.590; N2@DRIVE=1.59~1.590; Y@REF=1.06~1.062; D1@BORE=0.72~0.719; D2@BORE=0.72~0.719</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1871,7 +1907,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -1879,7 +1915,11 @@
           <t>Air-Way s127 only (double-pass 29 rows)</t>
         </is>
       </c>
-      <c r="M25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=1.97~1.970; N2@DRIVE=1.97~1.970; Y@REF=1.31~1.312; D1@BORE=0.94~0.938; D2@BORE=0.94~0.938</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2046,7 +2086,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2056,7 +2096,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>A(2) printed "1 1/2-11 1/2" both passes (a -20 end is 1 1/4-11 1/2; D2=1.25 supports 1 1/4) - as-printed, likely typo</t>
+          <t>A(2) printed "1 1/2-11 1/2" both passes (a -20 end is 1 1/4-11 1/2; D2=1.25 supports 1 1/4) - as-printed, likely typo | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on N1@DRIVE=2.38~2.380; N2@DRIVE=2.38~2.380; Y@REF=1.63~1.625; D1@BORE=1.25~1.250; D2@BORE=1.25~1.250</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_5500.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5500.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0.44</v>
@@ -586,12 +586,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s127 only (double-pass 29 rows); N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]; N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]</t>
+          <t>Air-Way s127 only (double-pass 29 rows); N1@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]; N2@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1432 = 0.780 (table had 0.72) [user 2026-10-18 A19]; N1@DRIVE: Air-Way 0.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; N2@DRIVE: Air-Way 0.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.78) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): N1@DRIVE 0.72 -&gt; OMi 0.780 (Items!N1432, M099) | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.72 -&gt; OMi 0.780 (Items!P1432, M100)</t>
+          <t>A19 (user 2026-10-18, group 2 settled): N1@DRIVE 0.72 -&gt; OMi 0.780 (Items!N1432, M099) | A19 (user 2026-10-18, group 2 settled): N2@DRIVE 0.72 -&gt; OMi 0.780 (Items!P1432, M100) | 2026-10-20 Air-Way first: N1@DRIVE OMi/Brennan 0.78 -&gt; Air-Way 0.72 | 2026-10-20 Air-Way first: N2@DRIVE OMi/Brennan 0.78 -&gt; Air-Way 0.72</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2239,7 +2239,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>1.94</v>
@@ -2270,10 +2270,14 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s127 only (double-pass 29 rows); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1448 Hex Flat = 2.500 (table had 2.58) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr"/>
+          <t>Air-Way s127 only (double-pass 29 rows); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1448 Hex Flat = 2.500 (table had 2.58) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; Y@REF: Air-Way 2.58 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: Y@REF OMi/Brennan 2.5 -&gt; Air-Way 2.58</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>BUILD</t>
